--- a/data/threshold_p.xlsx
+++ b/data/threshold_p.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Joe/Documents/College/02- R code/2- heating/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC70C4B6-15A2-8E4B-855D-AC819ABBF7DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1433585B-B0BD-DA4B-95F2-6AD0758C0231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15740" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="June_2022" sheetId="1" r:id="rId1"/>
@@ -165,12 +165,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -185,8 +191,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -900,6 +908,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -1452,7 +1463,7 @@
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="2">
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="L4">
@@ -1575,7 +1586,7 @@
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>0.62</v>
       </c>
       <c r="L7">
@@ -1698,7 +1709,7 @@
       <c r="J10">
         <v>0</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0.66</v>
       </c>
       <c r="L10">
@@ -1739,7 +1750,7 @@
       <c r="J11">
         <v>0</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>0.24199999999999999</v>
       </c>
       <c r="L11">
@@ -1780,7 +1791,7 @@
       <c r="J12">
         <v>0</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>0.22800000000000001</v>
       </c>
       <c r="L12">
@@ -1799,6 +1810,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="13" width="16" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -1872,7 +1886,7 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0.50509999999999999</v>
       </c>
       <c r="L2">
@@ -1995,7 +2009,7 @@
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0.13730000000000001</v>
       </c>
       <c r="L5">
@@ -2077,7 +2091,7 @@
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>0.98699999999999999</v>
       </c>
       <c r="L7">
@@ -2118,7 +2132,7 @@
       <c r="J8">
         <v>0</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>0.60760000000000003</v>
       </c>
       <c r="L8">
@@ -2200,7 +2214,7 @@
       <c r="J10">
         <v>0</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0.22520000000000001</v>
       </c>
       <c r="L10">
@@ -2241,7 +2255,7 @@
       <c r="J11">
         <v>0</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>0.996</v>
       </c>
       <c r="L11">
@@ -2282,7 +2296,7 @@
       <c r="J12">
         <v>0</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>0.252</v>
       </c>
       <c r="L12">
@@ -2301,6 +2315,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="10" width="16.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">

--- a/data/threshold_p.xlsx
+++ b/data/threshold_p.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Joe/Documents/College/02- R code/2- heating/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1433585B-B0BD-DA4B-95F2-6AD0758C0231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72DBBD99-32AA-BB45-A363-39EF159EBBFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15740" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="43">
   <si>
     <t>species</t>
   </si>
@@ -150,6 +150,9 @@
   </si>
   <si>
     <t>September 2023 (T95)</t>
+  </si>
+  <si>
+    <t>Ulmus rubra</t>
   </si>
 </sst>
 </file>
@@ -191,10 +194,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1463,7 +1465,7 @@
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4">
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="L4">
@@ -2673,7 +2675,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="B12">
         <v>0.74180000000000001</v>

--- a/data/threshold_p.xlsx
+++ b/data/threshold_p.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Joe/Documents/College/02- R code/2- heating/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\heat_tolerance\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72DBBD99-32AA-BB45-A363-39EF159EBBFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C16AF16-2EAA-42C9-A033-D2D1D099BF6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15740" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25710" yWindow="375" windowWidth="24090" windowHeight="19200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="June_2022" sheetId="1" r:id="rId1"/>
@@ -512,12 +512,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="10" width="16.33203125" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -549,7 +553,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -581,7 +585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -613,7 +617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -645,7 +649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -677,7 +681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -709,7 +713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -741,7 +745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -773,7 +777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -805,7 +809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -837,7 +841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -869,7 +873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -909,12 +913,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -946,7 +959,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -978,7 +991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1010,7 +1023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1042,7 +1055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1074,7 +1087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1106,7 +1119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -1138,7 +1151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1170,7 +1183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1202,7 +1215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1234,7 +1247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1266,7 +1279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1306,12 +1319,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="13" width="15.5" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="13" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1352,7 +1368,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1393,7 +1409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1434,7 +1450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1475,7 +1491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1516,7 +1532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1557,7 +1573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -1598,7 +1614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1639,7 +1655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1680,7 +1696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1721,7 +1737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1762,7 +1778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1811,12 +1827,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:M12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="13" width="16" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="13" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1857,7 +1877,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1898,7 +1918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1939,7 +1959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1980,7 +2000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -2021,7 +2041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -2062,7 +2082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -2103,7 +2123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -2144,7 +2164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -2185,7 +2205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -2226,7 +2246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2267,7 +2287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -2316,12 +2336,21 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="10" width="16.33203125" customWidth="1"/>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2353,7 +2382,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -2385,7 +2414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -2417,7 +2446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2449,7 +2478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -2481,7 +2510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -2513,7 +2542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -2545,7 +2574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -2577,7 +2606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -2609,7 +2638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -2641,7 +2670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2673,7 +2702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>42</v>
       </c>

--- a/data/threshold_p.xlsx
+++ b/data/threshold_p.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\heat_tolerance\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C16AF16-2EAA-42C9-A033-D2D1D099BF6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50BDF5F3-2082-4738-AFA5-464D8CA2E716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25710" yWindow="375" windowWidth="24090" windowHeight="19200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="510" yWindow="690" windowWidth="35265" windowHeight="19275" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="June_2022" sheetId="1" r:id="rId1"/>
@@ -18,13 +18,18 @@
     <sheet name="July_2022" sheetId="3" r:id="rId3"/>
     <sheet name="July_2023" sheetId="4" r:id="rId4"/>
     <sheet name="Sept_2023" sheetId="5" r:id="rId5"/>
+    <sheet name="leaf_June_2022" sheetId="7" r:id="rId6"/>
+    <sheet name="leaf_July_2022" sheetId="8" r:id="rId7"/>
+    <sheet name="leaf_June_2023" sheetId="9" r:id="rId8"/>
+    <sheet name="leaf_July_2023" sheetId="10" r:id="rId9"/>
+    <sheet name="Leaf temperature table" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="60">
   <si>
     <t>species</t>
   </si>
@@ -153,6 +158,57 @@
   </si>
   <si>
     <t>Ulmus rubra</t>
+  </si>
+  <si>
+    <t>Leaf June 22(tcrit)</t>
+  </si>
+  <si>
+    <t>Leaf June 22 (T50)</t>
+  </si>
+  <si>
+    <t>Leaf June 22 (T95)</t>
+  </si>
+  <si>
+    <t>Leaf July 22(tcrit)</t>
+  </si>
+  <si>
+    <t>Leaf July 22 (T50)</t>
+  </si>
+  <si>
+    <t>Leaf July 22 (T95)</t>
+  </si>
+  <si>
+    <t>Leaf June 23(tcrit)</t>
+  </si>
+  <si>
+    <t>Leaf June 23 (T50)</t>
+  </si>
+  <si>
+    <t>Leaf June 23 (T95)</t>
+  </si>
+  <si>
+    <t>Leaf July 23(tcrit)</t>
+  </si>
+  <si>
+    <t>Leaf July 23 (T50)</t>
+  </si>
+  <si>
+    <t>Leaf July 23 (T95)</t>
+  </si>
+  <si>
+    <t>Species</t>
+  </si>
+  <si>
+    <t>&lt;0.001</t>
+  </si>
+  <si>
+    <t>&gt;0.999</t>
+  </si>
+  <si>
+    <t>Leaf temperature 2022</t>
+  </si>
+  <si>
+    <t>Leaf temperature 2023</t>
   </si>
 </sst>
 </file>
@@ -510,15 +566,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A23EA5-2325-434B-921E-4888F3AE2CCE}">
   <dimension ref="A1:J12"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="16.28515625" customWidth="1"/>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="18.140625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="18.140625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -903,6 +964,234 @@
       </c>
       <c r="J12">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC6A3F6-6EE5-46A3-BDCC-C293A1205373}">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="G2">
+        <v>0.50509999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4">
+        <v>0.79200000000000004</v>
+      </c>
+      <c r="E4">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="F4">
+        <v>0.48</v>
+      </c>
+      <c r="G4">
+        <v>8.4000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0.13730000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>1E-3</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>1E-3</v>
+      </c>
+      <c r="G6">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>0.73899999999999999</v>
+      </c>
+      <c r="E7">
+        <v>0.62</v>
+      </c>
+      <c r="F7">
+        <v>0.996</v>
+      </c>
+      <c r="G7">
+        <v>0.98699999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0.5575</v>
+      </c>
+      <c r="G8">
+        <v>0.60760000000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="E9">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="F9">
+        <v>0.3206</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10">
+        <v>0.126</v>
+      </c>
+      <c r="E10">
+        <v>0.66</v>
+      </c>
+      <c r="F10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10">
+        <v>0.22520000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11">
+        <v>0.16220000000000001</v>
+      </c>
+      <c r="E11">
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>0.996</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12">
+        <v>0.96679999999999999</v>
+      </c>
+      <c r="E12">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="F12">
+        <v>0.54449999999999998</v>
+      </c>
+      <c r="G12">
+        <v>0.252</v>
       </c>
     </row>
   </sheetData>
@@ -911,20 +1200,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D53B27CB-D8BB-4E46-ADAD-0AE8D850274C}">
   <dimension ref="A1:J12"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="18.140625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="18.140625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -1317,14 +1606,14 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9D90E0E-E5C9-4C00-871A-58F89E091DCC}">
   <dimension ref="A1:M12"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="15.42578125" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="13" width="15.42578125" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1825,15 +2114,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1B08285-B35B-489F-81DD-B5CF4588D20B}">
   <dimension ref="A1:M12"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="13" width="16" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="13" width="16" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -2334,20 +2623,20 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF94F7A4-A0CB-421F-90FD-0E0386F20B78}">
   <dimension ref="A1:J12"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="24.85546875" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="21" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="18.140625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="24.28515625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="20.42578125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="18.140625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="24.28515625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="20.42578125" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2737,4 +3026,731 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61FF9E2E-0CBB-41EF-B66E-C880883327CE}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>0.79200000000000004</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6">
+        <v>1E-3</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7">
+        <v>0.73899999999999999</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>0.126</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11">
+        <v>0.16220000000000001</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12">
+        <v>0.96679999999999999</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82411354-F273-4155-8CD9-88615BC0F50E}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="16" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7">
+        <v>0.62</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>0.66</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11">
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A93065-8F95-4CD1-98BD-E65F1389D409}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>0.48</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6">
+        <v>1E-3</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7">
+        <v>0.996</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8">
+        <v>0.5575</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>0.3206</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12">
+        <v>0.54449999999999998</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20164656-928B-4E0C-ACE5-CCF2597F73FF}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2">
+        <v>0.50509999999999999</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5">
+        <v>0.13730000000000001</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6">
+        <v>1.4E-2</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7">
+        <v>0.98699999999999999</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8">
+        <v>0.60760000000000003</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>0.22520000000000001</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11">
+        <v>0.996</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12">
+        <v>0.252</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/threshold_p.xlsx
+++ b/data/threshold_p.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R\heat_tolerance\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Joe/Documents/College/02- R code/2- heating/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50BDF5F3-2082-4738-AFA5-464D8CA2E716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D22A1D3-89AF-064F-AA21-CBA611ED3E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="510" yWindow="690" windowWidth="35265" windowHeight="19275" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="June_2022" sheetId="1" r:id="rId1"/>
@@ -23,13 +23,30 @@
     <sheet name="leaf_June_2023" sheetId="9" r:id="rId8"/>
     <sheet name="leaf_July_2023" sheetId="10" r:id="rId9"/>
     <sheet name="Leaf temperature table" sheetId="11" r:id="rId10"/>
+    <sheet name="Air temperature table" sheetId="12" r:id="rId11"/>
+    <sheet name="Thermal Safety Margins" sheetId="13" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Air temperature table'!$B$2:$M$13</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="78">
   <si>
     <t>species</t>
   </si>
@@ -205,18 +222,83 @@
     <t>&gt;0.999</t>
   </si>
   <si>
-    <t>Leaf temperature 2022</t>
-  </si>
-  <si>
-    <t>Leaf temperature 2023</t>
+    <t>Leaf temperatures</t>
+  </si>
+  <si>
+    <t>June 2022</t>
+  </si>
+  <si>
+    <t>July 2022</t>
+  </si>
+  <si>
+    <t>June 2023</t>
+  </si>
+  <si>
+    <t>July 2023</t>
+  </si>
+  <si>
+    <t>Sample period</t>
+  </si>
+  <si>
+    <t>Record high</t>
+  </si>
+  <si>
+    <t>Record June high</t>
+  </si>
+  <si>
+    <t>Record July high</t>
+  </si>
+  <si>
+    <t>June 2023 high</t>
+  </si>
+  <si>
+    <t>July 2023 high</t>
+  </si>
+  <si>
+    <t>July 2022 high</t>
+  </si>
+  <si>
+    <t>June 2022 high</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>leaf_temp</t>
+  </si>
+  <si>
+    <t>mean_tcrit</t>
+  </si>
+  <si>
+    <t>difference</t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
+  <si>
+    <t>July</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
@@ -250,14 +332,389 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="35">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -568,21 +1025,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11A23EA5-2325-434B-921E-4888F3AE2CCE}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="18.140625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="18.140625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="15.1640625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="18.1640625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="18.5" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="18.1640625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.5" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -614,7 +1071,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -646,7 +1103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -678,7 +1135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -710,7 +1167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -742,7 +1199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -774,7 +1231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -806,7 +1263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -838,7 +1295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -870,7 +1327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -902,7 +1359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -934,7 +1391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -973,225 +1430,1895 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEC6A3F6-6EE5-46A3-BDCC-C293A1205373}">
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="8"/>
+      <c r="D1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2">
+        <v>2022</v>
+      </c>
+      <c r="C2">
+        <v>2023</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="C3">
+        <v>43.5</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0.50700000000000001</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0.50509999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4">
+        <v>38.9</v>
+      </c>
+      <c r="C4">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="D4" s="5">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="5">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5">
+        <v>45.3</v>
+      </c>
+      <c r="C5">
+        <v>41</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0.79200000000000004</v>
+      </c>
+      <c r="E5" s="5">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0.48</v>
+      </c>
+      <c r="G5" s="5">
+        <v>8.4000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6">
+        <v>37.6</v>
+      </c>
+      <c r="C6">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0.13730000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7">
+        <v>36.5</v>
+      </c>
+      <c r="C7">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1E-3</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1E-3</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8">
+        <v>44.5</v>
+      </c>
+      <c r="C8">
+        <v>44.8</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0.73899999999999999</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0.62</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0.996</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0.98699999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9">
+        <v>40.6</v>
+      </c>
+      <c r="C9">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0.5575</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0.60760000000000003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="C10">
+        <v>39.5</v>
+      </c>
+      <c r="D10" s="5">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="E10" s="5">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0.3206</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11">
+        <v>45.7</v>
+      </c>
+      <c r="C11">
+        <v>43.5</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0.126</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0.66</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0.22520000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12">
+        <v>41.9</v>
+      </c>
+      <c r="C12">
+        <v>45.3</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0.16220000000000001</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0.24199999999999999</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0.996</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13">
+        <v>45.9</v>
+      </c>
+      <c r="C13">
+        <v>42.1</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0.96679999999999999</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0.54449999999999998</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0.252</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{382F61A7-F99D-9344-84FD-F56A521D9225}">
+  <dimension ref="A1:M29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="13" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="C3" s="4">
+        <v>1.9E-2</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0.16220000000000001</v>
+      </c>
+      <c r="F3" s="5">
+        <v>1.9E-2</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0.35599999999999998</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0.60570000000000002</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0.43390000000000001</v>
+      </c>
+      <c r="M3" s="5">
+        <v>3.56E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.41699999999999998</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0.90100000000000002</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0.65</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0.54800000000000004</v>
+      </c>
+      <c r="L4" s="5">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.56399999999999995</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.157</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1E-3</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0.96699999999999997</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0.81699999999999995</v>
+      </c>
+      <c r="J5" s="5">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0.51900000000000002</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="M5" s="5">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.93200000000000005</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.64100000000000001</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="5">
+        <v>3.4200000000000001E-2</v>
+      </c>
+      <c r="F6" s="5">
+        <v>2E-3</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0.37269999999999998</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0.28860000000000002</v>
+      </c>
+      <c r="M6" s="5">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.73499999999999999</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1E-3</v>
+      </c>
+      <c r="E7" s="5">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="F7" s="5">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0.44400000000000001</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0.156</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0.82099999999999995</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0.63900000000000001</v>
+      </c>
+      <c r="M7" s="5">
+        <v>7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="4">
+        <v>0.73899999999999999</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0.39600000000000002</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0.62</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0.19</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0.996</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0.215</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0.97299999999999998</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0.86</v>
+      </c>
+      <c r="M8" s="5">
+        <v>3.4000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="4">
+        <v>0.496</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0.13300000000000001</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0.91959999999999997</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0.81789999999999996</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0.17699999999999999</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0.93689999999999996</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0.8659</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0.2452</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="4">
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="C10" s="4">
+        <v>0.626</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0.16320000000000001</v>
+      </c>
+      <c r="F10" s="5">
+        <v>5.5100000000000003E-2</v>
+      </c>
+      <c r="G10" s="5">
+        <v>2E-3</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0.47439999999999999</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0.28339999999999999</v>
+      </c>
+      <c r="K10" s="5">
+        <v>2.3E-3</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="4">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1E-3</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0.498</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0.28299999999999997</v>
+      </c>
+      <c r="G11" s="5">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0.26700000000000002</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0.41139999999999999</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0.14910000000000001</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="4">
+        <v>0.60660000000000003</v>
+      </c>
+      <c r="C12" s="4">
+        <v>0.30930000000000002</v>
+      </c>
+      <c r="D12" s="5">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0.317</v>
+      </c>
+      <c r="G12" s="5">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0.94799999999999995</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0.96399999999999997</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0.56299999999999994</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="4">
+        <v>0.91049999999999998</v>
+      </c>
+      <c r="C13" s="4">
+        <v>0.78669999999999995</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0.19320000000000001</v>
+      </c>
+      <c r="E13" s="5">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="G13" s="5">
+        <v>1E-3</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0.85289999999999999</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0.67869999999999997</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0.15720000000000001</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0.38900000000000001</v>
+      </c>
+      <c r="M13" s="5">
+        <v>3.2000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:M1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B3:M13">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
+      <formula>0.051</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"&lt;0.001"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9316890-E486-E944-88ED-19733CF87EA7}">
+  <dimension ref="A1:F46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="19.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>55</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="C1" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="D1" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="E1" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="F1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
-        <v>56</v>
+      <c r="B2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2">
+        <v>2022</v>
+      </c>
+      <c r="D2">
+        <v>38.799999999999997</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>47.3</v>
       </c>
       <c r="F2">
-        <v>0.50700000000000001</v>
-      </c>
-      <c r="G2">
-        <v>0.50509999999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <f>E2-D2</f>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
+      <c r="B3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3">
+        <v>2022</v>
+      </c>
       <c r="D3">
-        <v>3.0000000000000001E-3</v>
+        <v>38.9</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>44.8</v>
       </c>
       <c r="F3">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <f>E3-D3</f>
+        <v>5.8999999999999986</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
+      <c r="B4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4">
+        <v>2022</v>
+      </c>
       <c r="D4">
-        <v>0.79200000000000004</v>
+        <v>45.3</v>
       </c>
       <c r="E4">
-        <v>2.5999999999999999E-2</v>
+        <v>44.3</v>
       </c>
       <c r="F4">
-        <v>0.48</v>
-      </c>
-      <c r="G4">
-        <v>8.4000000000000005E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <f>E4-D4</f>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>13</v>
       </c>
+      <c r="B5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5">
+        <v>2022</v>
+      </c>
       <c r="D5">
-        <v>0</v>
+        <v>37.6</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>42.5</v>
       </c>
       <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0.13730000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <f>E5-D5</f>
+        <v>4.8999999999999986</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
+      <c r="B6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6">
+        <v>2022</v>
+      </c>
       <c r="D6">
-        <v>1E-3</v>
+        <v>36.5</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>43.5</v>
       </c>
       <c r="F6">
-        <v>1E-3</v>
-      </c>
-      <c r="G6">
-        <v>1.4E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <f>E6-D6</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
+      <c r="B7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7">
+        <v>2022</v>
+      </c>
       <c r="D7">
-        <v>0.73899999999999999</v>
+        <v>44.5</v>
       </c>
       <c r="E7">
-        <v>0.62</v>
+        <v>43.4</v>
       </c>
       <c r="F7">
-        <v>0.996</v>
-      </c>
-      <c r="G7">
-        <v>0.98699999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <f>E7-D7</f>
+        <v>-1.1000000000000014</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
+      <c r="B8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8">
+        <v>2022</v>
+      </c>
       <c r="D8">
-        <v>0</v>
+        <v>40.6</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>44.5</v>
       </c>
       <c r="F8">
-        <v>0.5575</v>
-      </c>
-      <c r="G8">
-        <v>0.60760000000000003</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <f>E8-D8</f>
+        <v>3.8999999999999986</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
+      <c r="B9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9">
+        <v>2022</v>
+      </c>
       <c r="D9">
-        <v>2.1000000000000001E-2</v>
+        <v>40.200000000000003</v>
       </c>
       <c r="E9">
-        <v>7.0000000000000001E-3</v>
+        <v>42.6</v>
       </c>
       <c r="F9">
-        <v>0.3206</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <f>E9-D9</f>
+        <v>2.3999999999999986</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
+      <c r="B10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10">
+        <v>2022</v>
+      </c>
       <c r="D10">
-        <v>0.126</v>
+        <v>45.7</v>
       </c>
       <c r="E10">
-        <v>0.66</v>
-      </c>
-      <c r="F10" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10">
-        <v>0.22520000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>46.5</v>
+      </c>
+      <c r="F10">
+        <f>E10-D10</f>
+        <v>0.79999999999999716</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
+      <c r="B11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11">
+        <v>2022</v>
+      </c>
       <c r="D11">
-        <v>0.16220000000000001</v>
+        <v>41.9</v>
       </c>
       <c r="E11">
-        <v>0.24199999999999999</v>
+        <v>44</v>
       </c>
       <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>0.996</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <f>E11-D11</f>
+        <v>2.1000000000000014</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>42</v>
       </c>
+      <c r="B12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12">
+        <v>2022</v>
+      </c>
       <c r="D12">
-        <v>0.96679999999999999</v>
+        <v>45.9</v>
       </c>
       <c r="E12">
-        <v>0.22800000000000001</v>
+        <v>40.6</v>
       </c>
       <c r="F12">
-        <v>0.54449999999999998</v>
-      </c>
-      <c r="G12">
-        <v>0.252</v>
+        <f>E12-D12</f>
+        <v>-5.2999999999999972</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13">
+        <v>2022</v>
+      </c>
+      <c r="D13">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="E13">
+        <v>46.1</v>
+      </c>
+      <c r="F13">
+        <f>E13-D13</f>
+        <v>7.3000000000000043</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14">
+        <v>2022</v>
+      </c>
+      <c r="D14">
+        <v>38.9</v>
+      </c>
+      <c r="E14">
+        <v>47.9</v>
+      </c>
+      <c r="F14">
+        <f>E14-D14</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15">
+        <v>2022</v>
+      </c>
+      <c r="D15">
+        <v>45.3</v>
+      </c>
+      <c r="E15">
+        <v>47.9</v>
+      </c>
+      <c r="F15">
+        <f>E15-D15</f>
+        <v>2.6000000000000014</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16">
+        <v>2022</v>
+      </c>
+      <c r="D16">
+        <v>37.6</v>
+      </c>
+      <c r="E16">
+        <v>47.5</v>
+      </c>
+      <c r="F16">
+        <f>E16-D16</f>
+        <v>9.8999999999999986</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17">
+        <v>2022</v>
+      </c>
+      <c r="D17">
+        <v>36.5</v>
+      </c>
+      <c r="E17">
+        <v>46.2</v>
+      </c>
+      <c r="F17">
+        <f>E17-D17</f>
+        <v>9.7000000000000028</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18">
+        <v>2022</v>
+      </c>
+      <c r="D18">
+        <v>44.5</v>
+      </c>
+      <c r="E18">
+        <v>44.2</v>
+      </c>
+      <c r="F18">
+        <f>E18-D18</f>
+        <v>-0.29999999999999716</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19">
+        <v>2022</v>
+      </c>
+      <c r="D19">
+        <v>40.6</v>
+      </c>
+      <c r="E19">
+        <v>48.5</v>
+      </c>
+      <c r="F19">
+        <f>E19-D19</f>
+        <v>7.8999999999999986</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20">
+        <v>2022</v>
+      </c>
+      <c r="D20">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="E20">
+        <v>46.3</v>
+      </c>
+      <c r="F20">
+        <f>E20-D20</f>
+        <v>6.0999999999999943</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21">
+        <v>2022</v>
+      </c>
+      <c r="D21">
+        <v>45.7</v>
+      </c>
+      <c r="E21">
+        <v>44.1</v>
+      </c>
+      <c r="F21">
+        <f>E21-D21</f>
+        <v>-1.6000000000000014</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22">
+        <v>2022</v>
+      </c>
+      <c r="D22">
+        <v>41.9</v>
+      </c>
+      <c r="E22">
+        <v>43.9</v>
+      </c>
+      <c r="F22">
+        <f>E22-D22</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23">
+        <v>2022</v>
+      </c>
+      <c r="D23">
+        <v>45.9</v>
+      </c>
+      <c r="E23">
+        <v>47.5</v>
+      </c>
+      <c r="F23">
+        <f>E23-D23</f>
+        <v>1.6000000000000014</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25">
+        <v>2023</v>
+      </c>
+      <c r="D25">
+        <v>43.5</v>
+      </c>
+      <c r="E25">
+        <v>43.7</v>
+      </c>
+      <c r="F25">
+        <f>E25-D25</f>
+        <v>0.20000000000000284</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26">
+        <v>2023</v>
+      </c>
+      <c r="D26">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="E26">
+        <v>42.4</v>
+      </c>
+      <c r="F26">
+        <f>E26-D26</f>
+        <v>3.6999999999999957</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27">
+        <v>2023</v>
+      </c>
+      <c r="D27">
+        <v>41</v>
+      </c>
+      <c r="E27">
+        <v>41.1</v>
+      </c>
+      <c r="F27">
+        <f>E27-D27</f>
+        <v>0.10000000000000142</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28">
+        <v>2023</v>
+      </c>
+      <c r="D28">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="E28">
+        <v>46.4</v>
+      </c>
+      <c r="F28">
+        <f>E28-D28</f>
+        <v>5.6000000000000014</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29">
+        <v>2023</v>
+      </c>
+      <c r="D29">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="E29">
+        <v>45.3</v>
+      </c>
+      <c r="F29">
+        <f>E29-D29</f>
+        <v>6.5999999999999943</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>76</v>
+      </c>
+      <c r="C30">
+        <v>2023</v>
+      </c>
+      <c r="D30">
+        <v>44.8</v>
+      </c>
+      <c r="E30">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="F30">
+        <f>E30-D30</f>
+        <v>-5.5999999999999943</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31">
+        <v>2023</v>
+      </c>
+      <c r="D31">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="E31">
+        <v>40.4</v>
+      </c>
+      <c r="F31">
+        <f>E31-D31</f>
+        <v>-0.30000000000000426</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32">
+        <v>2023</v>
+      </c>
+      <c r="D32">
+        <v>39.5</v>
+      </c>
+      <c r="E32">
+        <v>42.2</v>
+      </c>
+      <c r="F32">
+        <f>E32-D32</f>
+        <v>2.7000000000000028</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33" t="s">
+        <v>76</v>
+      </c>
+      <c r="C33">
+        <v>2023</v>
+      </c>
+      <c r="D33">
+        <v>43.5</v>
+      </c>
+      <c r="E33">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="F33">
+        <f>E33-D33</f>
+        <v>-4.7999999999999972</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" t="s">
+        <v>76</v>
+      </c>
+      <c r="C34">
+        <v>2023</v>
+      </c>
+      <c r="D34">
+        <v>45.3</v>
+      </c>
+      <c r="E34">
+        <v>41.9</v>
+      </c>
+      <c r="F34">
+        <f>E34-D34</f>
+        <v>-3.3999999999999986</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35">
+        <v>2023</v>
+      </c>
+      <c r="D35">
+        <v>42.1</v>
+      </c>
+      <c r="E35">
+        <v>41.2</v>
+      </c>
+      <c r="F35">
+        <f>E35-D35</f>
+        <v>-0.89999999999999858</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36">
+        <v>2023</v>
+      </c>
+      <c r="D36">
+        <v>43.5</v>
+      </c>
+      <c r="E36">
+        <v>43.7</v>
+      </c>
+      <c r="F36">
+        <f>E36-D36</f>
+        <v>0.20000000000000284</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" t="s">
+        <v>77</v>
+      </c>
+      <c r="C37">
+        <v>2023</v>
+      </c>
+      <c r="D37">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="E37">
+        <v>44.4</v>
+      </c>
+      <c r="F37">
+        <f>E37-D37</f>
+        <v>5.6999999999999957</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38">
+        <v>2023</v>
+      </c>
+      <c r="D38">
+        <v>41</v>
+      </c>
+      <c r="E38">
+        <v>44.2</v>
+      </c>
+      <c r="F38">
+        <f>E38-D38</f>
+        <v>3.2000000000000028</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39">
+        <v>2023</v>
+      </c>
+      <c r="D39">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="E39">
+        <v>45.5</v>
+      </c>
+      <c r="F39">
+        <f>E39-D39</f>
+        <v>4.7000000000000028</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" t="s">
+        <v>77</v>
+      </c>
+      <c r="C40">
+        <v>2023</v>
+      </c>
+      <c r="D40">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="E40">
+        <v>42.7</v>
+      </c>
+      <c r="F40">
+        <f>E40-D40</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>77</v>
+      </c>
+      <c r="C41">
+        <v>2023</v>
+      </c>
+      <c r="D41">
+        <v>44.8</v>
+      </c>
+      <c r="E41">
+        <v>41.2</v>
+      </c>
+      <c r="F41">
+        <f>E41-D41</f>
+        <v>-3.5999999999999943</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>16</v>
+      </c>
+      <c r="B42" t="s">
+        <v>77</v>
+      </c>
+      <c r="C42">
+        <v>2023</v>
+      </c>
+      <c r="D42">
+        <v>40.700000000000003</v>
+      </c>
+      <c r="E42">
+        <v>39.9</v>
+      </c>
+      <c r="F42">
+        <f>E42-D42</f>
+        <v>-0.80000000000000426</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>17</v>
+      </c>
+      <c r="B43" t="s">
+        <v>77</v>
+      </c>
+      <c r="C43">
+        <v>2023</v>
+      </c>
+      <c r="D43">
+        <v>39.5</v>
+      </c>
+      <c r="E43">
+        <v>49.1</v>
+      </c>
+      <c r="F43">
+        <f>E43-D43</f>
+        <v>9.6000000000000014</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" t="s">
+        <v>77</v>
+      </c>
+      <c r="C44">
+        <v>2023</v>
+      </c>
+      <c r="D44">
+        <v>43.5</v>
+      </c>
+      <c r="E44">
+        <v>44.8</v>
+      </c>
+      <c r="F44">
+        <f>E44-D44</f>
+        <v>1.2999999999999972</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>19</v>
+      </c>
+      <c r="B45" t="s">
+        <v>77</v>
+      </c>
+      <c r="C45">
+        <v>2023</v>
+      </c>
+      <c r="D45">
+        <v>45.3</v>
+      </c>
+      <c r="E45">
+        <v>42.8</v>
+      </c>
+      <c r="F45">
+        <f>E45-D45</f>
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>42</v>
+      </c>
+      <c r="B46" t="s">
+        <v>77</v>
+      </c>
+      <c r="C46">
+        <v>2023</v>
+      </c>
+      <c r="D46">
+        <v>42.1</v>
+      </c>
+      <c r="E46">
+        <v>43.9</v>
+      </c>
+      <c r="F46">
+        <f>E46-D46</f>
+        <v>1.7999999999999972</v>
       </c>
     </row>
   </sheetData>
@@ -1202,21 +3329,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D53B27CB-D8BB-4E46-ADAD-0AE8D850274C}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="18.140625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="18.140625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="15.1640625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="18.1640625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="18.5" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="14.5" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="18.1640625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.5" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="14.5" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1248,7 +3375,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1280,7 +3407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1312,7 +3439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1344,7 +3471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1376,7 +3503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1408,7 +3535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -1440,7 +3567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1472,7 +3599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1504,7 +3631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1536,7 +3663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1568,7 +3695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1608,15 +3735,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9D90E0E-E5C9-4C00-871A-58F89E091DCC}">
   <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="13" width="15.42578125" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="15.5" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="13" width="15.5" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1657,7 +3784,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1698,7 +3825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1739,7 +3866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1780,7 +3907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1821,7 +3948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1862,7 +3989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -1903,7 +4030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1944,7 +4071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1985,7 +4112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -2026,7 +4153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2067,7 +4194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -2116,16 +4243,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1B08285-B35B-489F-81DD-B5CF4588D20B}">
   <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="14.5" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="5" max="13" width="16" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2166,7 +4293,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -2207,7 +4334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -2248,7 +4375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2289,7 +4416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -2330,7 +4457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -2371,7 +4498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -2412,7 +4539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -2453,7 +4580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -2494,7 +4621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -2535,7 +4662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2576,7 +4703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -2625,21 +4752,21 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF94F7A4-A0CB-421F-90FD-0E0386F20B78}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="24.85546875" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="24.83203125" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="4" max="4" width="21" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="18.140625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="24.28515625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="20.42578125" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="18.140625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="24.28515625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="20.42578125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="18.1640625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="24.33203125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="20.5" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="18.1640625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="24.33203125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="20.5" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2671,7 +4798,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -2703,7 +4830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -2735,7 +4862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2767,7 +4894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -2799,7 +4926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -2831,7 +4958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -2863,7 +4990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -2895,7 +5022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -2927,7 +5054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -2959,7 +5086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2991,7 +5118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -3031,14 +5158,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61FF9E2E-0CBB-41EF-B66E-C880883327CE}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3052,7 +5179,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -3066,7 +5193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -3080,7 +5207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -3094,7 +5221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -3108,7 +5235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -3122,7 +5249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -3136,7 +5263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -3150,7 +5277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -3164,7 +5291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -3178,7 +5305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -3192,7 +5319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -3207,6 +5334,11 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="cellIs" dxfId="34" priority="1" operator="greaterThan">
+      <formula>0.9499</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3214,14 +5346,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82411354-F273-4155-8CD9-88615BC0F50E}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3235,7 +5367,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -3249,7 +5381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -3263,7 +5395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -3277,7 +5409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -3291,7 +5423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -3305,7 +5437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -3319,7 +5451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -3333,7 +5465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -3347,7 +5479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -3361,7 +5493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -3375,7 +5507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -3390,6 +5522,11 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B1:B12">
+    <cfRule type="cellIs" dxfId="33" priority="1" operator="greaterThan">
+      <formula>0.9499</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3397,14 +5534,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A93065-8F95-4CD1-98BD-E65F1389D409}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3418,7 +5555,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -3432,7 +5569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -3446,7 +5583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -3460,7 +5597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -3474,7 +5611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -3488,7 +5625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -3502,7 +5639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -3516,7 +5653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -3530,7 +5667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -3544,7 +5681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -3558,7 +5695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -3573,6 +5710,11 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B1:B12">
+    <cfRule type="cellIs" dxfId="32" priority="1" operator="greaterThan">
+      <formula>0.9499</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3580,9 +5722,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20164656-928B-4E0C-ACE5-CCF2597F73FF}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3596,7 +5738,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -3610,7 +5752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -3624,7 +5766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -3638,7 +5780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -3652,7 +5794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -3666,7 +5808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -3680,7 +5822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -3694,7 +5836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -3708,7 +5850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -3722,7 +5864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -3736,7 +5878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>42</v>
       </c>
